--- a/docs/Defect_Tracker.xlsx
+++ b/docs/Defect_Tracker.xlsx
@@ -449,20 +449,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="55" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="50" customWidth="1" min="11" max="11"/>
+    <col width="55" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -538,7 +538,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>FastAPI fails to launch due to sqlite3 version incompatibility with ChromaDB</t>
+          <t>ChromaDB throws sqlite3.OperationalError indicating SQLite 3.35+ is required on local system.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Installed pysqlite3-binary and configured patch in chromadb.py launcher</t>
+          <t>Installed pysqlite3-binary package and updated backend database initialization driver to monkeypatch system sqlite3 module.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -573,7 +573,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>Verified startup checks execute successfully</t>
+          <t>FastAPI server successfully starts up on local developer systems.</t>
         </is>
       </c>
     </row>
@@ -588,17 +588,17 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Large PyTorch imports during vector calculations crashRender container (OOM)</t>
+          <t>Customer Simulator node responses ignore target difficulty level and respond with identical word counts.</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Sprint 1</t>
+          <t>Sprint 2</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -608,17 +608,17 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Maintainability</t>
+          <t>Logical</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Built RAM environment detection to toggle fallback MongoDB keyword text indexes</t>
+          <t>Refactored simulator system prompt to enforce frustration ceilings and vocabulary length based on selected difficulty (easy, medium, hard).</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -628,7 +628,7 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>Render deployment operates cleanly under 512MB limit</t>
+          <t>Tested simulator mood adjustments across easy/hard scenarios.</t>
         </is>
       </c>
     </row>
@@ -643,17 +643,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Customer Simulator LLM node responds in generic terms disregarding target difficulty setting</t>
+          <t>LangGraph parallel analysis execution throws state override errors, replacing concurrent node dictionary entries.</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Sprint 2</t>
+          <t>Sprint 3</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -668,12 +668,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Refactored prompts to enforce strict customer reaction bounds and difficulty mappings</t>
+          <t>Implemented a custom list-appending state reducer function in state.py to join agent execution logs without collisions.</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>Verified customer mood progression adjusts accurately</t>
+          <t>State correctly merges parallel node intent/sentiment/risk records.</t>
         </is>
       </c>
     </row>
@@ -693,29 +693,29 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
+          <t>Priya Sharma</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Auto-FAQ generation creates duplicate draft entries when search gap query keywords overlap.</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>Tushar Agarwal</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>LangGraph parallel node execution updates overwrite other concurrent results in graph state</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Sprint 3</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Tushar Agarwal</t>
-        </is>
-      </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Logical</t>
@@ -723,12 +723,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Implemented a custom merge_logs state reducer function in LangGraph definitions</t>
+          <t>Added unique index constraint on FAQ MongoDB database collection and filtered overlapping draft requests before saving.</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -738,117 +738,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>Parallel node execution works seamlessly</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Priya Sharma</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>SSE token messages cutoff mid-sentence in suggestion box due to buffer limits</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Sprint 3</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Priya Sharma</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>User Interface</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Configured React stream reader hook to append and buffer string tokens cleanly</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>Verified streaming suggestions display correctly</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Priya Sharma</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>FAQ generation engine creates duplicates on overlapping keyword-gap inputs</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Sprint 4</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Tushar Agarwal</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>Logical</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>Added unique constraint check querying MongoDB collection prior to draft creation</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-22</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>Verified duplicate drafts are merged or rejected automatically</t>
+          <t>Checked and verified duplication filter operates cleanly.</t>
         </is>
       </c>
     </row>
